--- a/apps/platform/test-harness/aurora-primary/arbor-exports/sen_register_arbor.xlsx
+++ b/apps/platform/test-harness/aurora-primary/arbor-exports/sen_register_arbor.xlsx
@@ -1001,7 +1001,7 @@
         <v>EHCP Provision</v>
       </c>
       <c r="O10" t="str">
-        <v>Mr Edwards (STF-026)</v>
+        <v>Mrs Sharma (STF-035)</v>
       </c>
       <c r="P10" t="str">
         <v/>
@@ -1683,7 +1683,7 @@
         <v>EHCP Provision</v>
       </c>
       <c r="O21" t="str">
-        <v>Mrs Price (STF-025)</v>
+        <v>Mrs Ahmed (STF-027)</v>
       </c>
       <c r="P21" t="str">
         <v>Occupational Therapy</v>
@@ -2055,7 +2055,7 @@
         <v>EHCP Provision</v>
       </c>
       <c r="O27" t="str">
-        <v>Class Teacher</v>
+        <v>Miss Turner (STF-034)</v>
       </c>
       <c r="P27" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>EHCP Provision</v>
       </c>
       <c r="O28" t="str">
-        <v>Mr Edwards (STF-026)</v>
+        <v>Miss Turner (STF-034)</v>
       </c>
       <c r="P28" t="str">
         <v>CAMHS</v>
@@ -2303,7 +2303,7 @@
         <v>EHCP Provision</v>
       </c>
       <c r="O31" t="str">
-        <v>Class Teacher</v>
+        <v>Mrs Ahmed (STF-027)</v>
       </c>
       <c r="P31" t="str">
         <v/>
@@ -2365,7 +2365,7 @@
         <v>EHCP Provision</v>
       </c>
       <c r="O32" t="str">
-        <v>Mrs Price (STF-025)</v>
+        <v>Miss Turner (STF-034)</v>
       </c>
       <c r="P32" t="str">
         <v>CAMHS</v>
@@ -2551,7 +2551,7 @@
         <v>EHCP Provision</v>
       </c>
       <c r="O35" t="str">
-        <v>Class Teacher</v>
+        <v>Ms Okafor (STF-028)</v>
       </c>
       <c r="P35" t="str">
         <v/>
@@ -3047,7 +3047,7 @@
         <v>EHCP Provision</v>
       </c>
       <c r="O43" t="str">
-        <v>Mr Edwards (STF-026)</v>
+        <v>Ms Okafor (STF-028)</v>
       </c>
       <c r="P43" t="str">
         <v/>
@@ -3419,7 +3419,7 @@
         <v>EHCP Provision</v>
       </c>
       <c r="O49" t="str">
-        <v>Mrs Price (STF-025)</v>
+        <v>Mrs Khan (STF-029)</v>
       </c>
       <c r="P49" t="str">
         <v/>
@@ -3543,7 +3543,7 @@
         <v>EHCP Provision</v>
       </c>
       <c r="O51" t="str">
-        <v>Class Teacher</v>
+        <v>Mrs Khan (STF-029)</v>
       </c>
       <c r="P51" t="str">
         <v>CAMHS</v>
@@ -3853,7 +3853,7 @@
         <v>EHCP Provision</v>
       </c>
       <c r="O56" t="str">
-        <v>Class Teacher</v>
+        <v>Mrs Morris (STF-032)</v>
       </c>
       <c r="P56" t="str">
         <v/>
@@ -4907,7 +4907,7 @@
         <v>EHCP Provision</v>
       </c>
       <c r="O73" t="str">
-        <v>Class Teacher</v>
+        <v>Mrs Dixon (STF-036)</v>
       </c>
       <c r="P73" t="str">
         <v/>
@@ -5465,7 +5465,7 @@
         <v>EHCP Provision</v>
       </c>
       <c r="O82" t="str">
-        <v>Class Teacher</v>
+        <v>Mr Cooper (STF-031)</v>
       </c>
       <c r="P82" t="str">
         <v/>
@@ -5589,7 +5589,7 @@
         <v>EHCP Provision</v>
       </c>
       <c r="O84" t="str">
-        <v>Mr Edwards (STF-026)</v>
+        <v>Mr Cooper (STF-031)</v>
       </c>
       <c r="P84" t="str">
         <v/>
